--- a/10. Sistemas de gestion empresarial/HorasTrabajadas3Meses.xlsx
+++ b/10. Sistemas de gestion empresarial/HorasTrabajadas3Meses.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cheng\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cheng\Desktop\2DAM\10. Sistemas de gestion empresarial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C5360D6-95B0-4622-8E2C-0BEEFC7CACF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E63DF62E-3E2E-4624-A70D-AD75CF832BFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7410" yWindow="4950" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Horas trabajadas" sheetId="1" r:id="rId1"/>
@@ -1046,16 +1046,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>14287</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>71437</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>90487</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>147637</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
